--- a/workspace/spreadsheets/designs_front_b.xlsx
+++ b/workspace/spreadsheets/designs_front_b.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Designs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Designs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -602,6 +602,144 @@
           <t>Notes</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DSN-B-0001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>vibes_club_001.png</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pet</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ICU Nurse</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vibes Club</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Illustrated quote design</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3600x4800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Pending Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DSN-B-0002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>daily_culture_001.png</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pet</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ICU Nurse</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Daily Culture</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Illustrated quote design</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3600x4800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Pending Upload</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
